--- a/data-preprocessing/rpc-footprints/1 - Crops/Pesticides.xlsx
+++ b/data-preprocessing/rpc-footprints/1 - Crops/Pesticides.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr filterPrivacy="1" updateLinks="never" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA62C213-E10E-1142-ACE5-8211EFE3D875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC1BB1D-D7F1-7648-AC84-E2232B93E163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="14360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INFO" sheetId="117" r:id="rId1"/>
@@ -4102,9 +4102,9 @@
       <c r="C6" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="37" t="e">
-        <f>0.9753*GL6+0.02473*#REF!</f>
-        <v>#REF!</v>
+      <c r="D6" s="37">
+        <f>0.9753*GL6</f>
+        <v>10.63077</v>
       </c>
       <c r="AM6">
         <v>11.1</v>
@@ -8742,6 +8742,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="dokument" ma:contentTypeID="0x010100A603BB68AE5C0F4C908E70EB4D1DDDC3" ma:contentTypeVersion="15" ma:contentTypeDescription="Skapa ett nytt dokument." ma:contentTypeScope="" ma:versionID="bc1901b771652496ef02f4cbdf878f9e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="31ffec6e-e0c6-46d3-bf16-e7019fdf1f95" xmlns:ns4="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6c61e44642a1e9e2aad865b2f0b39e8f" ns3:_="" ns4:_="">
     <xsd:import namespace="31ffec6e-e0c6-46d3-bf16-e7019fdf1f95"/>
@@ -8976,24 +8993,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{627ED23C-5EEB-4F10-AA20-79B788D8342E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A16A6EDB-4C6A-433C-9B54-BF88B9AEEE87}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27BF0A1B-B2BC-4159-BD4C-213AA0853490}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9010,22 +9028,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A16A6EDB-4C6A-433C-9B54-BF88B9AEEE87}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{627ED23C-5EEB-4F10-AA20-79B788D8342E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>